--- a/research/traditional_assets/database/data/ireland/ireland_retail_online.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_retail_online.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.4</v>
+        <v>-0.136</v>
       </c>
       <c r="G2">
-        <v>-4.668021680216802</v>
+        <v>-0.714123006833713</v>
       </c>
       <c r="H2">
-        <v>-5.13550135501355</v>
+        <v>-0.7949886104783599</v>
       </c>
       <c r="I2">
-        <v>-5.582655826558266</v>
+        <v>-0.5580865603644647</v>
       </c>
       <c r="J2">
-        <v>-5.582655826558266</v>
+        <v>-0.5580865603644647</v>
       </c>
       <c r="K2">
-        <v>-60.6</v>
+        <v>-31.3</v>
       </c>
       <c r="L2">
-        <v>-8.211382113821138</v>
+        <v>-0.7129840546697039</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>40</v>
+        <v>23.6</v>
       </c>
       <c r="V2">
-        <v>0.3707136237256719</v>
+        <v>0.1446965052115267</v>
       </c>
       <c r="W2">
-        <v>-0.4190871369294606</v>
+        <v>-0.3260416666666667</v>
       </c>
       <c r="X2">
-        <v>0.1024905417542077</v>
+        <v>0.1636045127180368</v>
       </c>
       <c r="Y2">
-        <v>-0.5215776786836682</v>
+        <v>-0.4896461793847035</v>
       </c>
       <c r="Z2">
-        <v>0.06276577649260079</v>
+        <v>0.481359649122807</v>
       </c>
       <c r="AA2">
-        <v>-0.3503997278448717</v>
+        <v>-0.268640350877193</v>
       </c>
       <c r="AB2">
-        <v>0.08485155950357269</v>
+        <v>0.1459483326464355</v>
       </c>
       <c r="AC2">
-        <v>-0.4352512873484444</v>
+        <v>-0.4145886835236285</v>
       </c>
       <c r="AD2">
-        <v>35.2</v>
+        <v>31.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>35.2</v>
+        <v>31.9</v>
       </c>
       <c r="AG2">
-        <v>-4.799999999999997</v>
+        <v>8.299999999999997</v>
       </c>
       <c r="AH2">
-        <v>0.2459818308874912</v>
+        <v>0.1635897435897436</v>
       </c>
       <c r="AI2">
-        <v>0.2682926829268293</v>
+        <v>0.3608597285067873</v>
       </c>
       <c r="AJ2">
-        <v>-0.046556741028128</v>
+        <v>0.0484247374562427</v>
       </c>
       <c r="AK2">
-        <v>-0.05263157894736839</v>
+        <v>0.1280864197530864</v>
       </c>
       <c r="AL2">
-        <v>1.79</v>
+        <v>4.33</v>
       </c>
       <c r="AM2">
-        <v>1.79</v>
+        <v>4.33</v>
       </c>
       <c r="AN2">
-        <v>-0.9072164948453609</v>
+        <v>-1.194756554307116</v>
       </c>
       <c r="AO2">
-        <v>-23.01675977653631</v>
+        <v>-5.658198614318707</v>
       </c>
       <c r="AP2">
-        <v>0.1237113402061855</v>
+        <v>-0.3108614232209737</v>
       </c>
       <c r="AQ2">
-        <v>-23.01675977653631</v>
+        <v>-5.658198614318707</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.4</v>
+        <v>-0.136</v>
       </c>
       <c r="G3">
-        <v>-4.668021680216802</v>
+        <v>-0.714123006833713</v>
       </c>
       <c r="H3">
-        <v>-5.13550135501355</v>
+        <v>-0.7949886104783599</v>
       </c>
       <c r="I3">
-        <v>-5.582655826558266</v>
+        <v>-0.5580865603644647</v>
       </c>
       <c r="J3">
-        <v>-5.582655826558266</v>
+        <v>-0.5580865603644647</v>
       </c>
       <c r="K3">
-        <v>-60.6</v>
+        <v>-31.3</v>
       </c>
       <c r="L3">
-        <v>-8.211382113821138</v>
+        <v>-0.7129840546697039</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>40</v>
+        <v>23.6</v>
       </c>
       <c r="V3">
-        <v>0.3707136237256719</v>
+        <v>0.1446965052115267</v>
       </c>
       <c r="W3">
-        <v>-0.4190871369294606</v>
+        <v>-0.3260416666666667</v>
       </c>
       <c r="X3">
-        <v>0.1024905417542077</v>
+        <v>0.1636045127180368</v>
       </c>
       <c r="Y3">
-        <v>-0.5215776786836682</v>
+        <v>-0.4896461793847035</v>
       </c>
       <c r="Z3">
-        <v>0.06276577649260079</v>
+        <v>0.481359649122807</v>
       </c>
       <c r="AA3">
-        <v>-0.3503997278448717</v>
+        <v>-0.268640350877193</v>
       </c>
       <c r="AB3">
-        <v>0.08485155950357269</v>
+        <v>0.1459483326464355</v>
       </c>
       <c r="AC3">
-        <v>-0.4352512873484444</v>
+        <v>-0.4145886835236285</v>
       </c>
       <c r="AD3">
-        <v>35.2</v>
+        <v>31.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>35.2</v>
+        <v>31.9</v>
       </c>
       <c r="AG3">
-        <v>-4.799999999999997</v>
+        <v>8.299999999999997</v>
       </c>
       <c r="AH3">
-        <v>0.2459818308874912</v>
+        <v>0.1635897435897436</v>
       </c>
       <c r="AI3">
-        <v>0.2682926829268293</v>
+        <v>0.3608597285067873</v>
       </c>
       <c r="AJ3">
-        <v>-0.046556741028128</v>
+        <v>0.0484247374562427</v>
       </c>
       <c r="AK3">
-        <v>-0.05263157894736839</v>
+        <v>0.1280864197530864</v>
       </c>
       <c r="AL3">
-        <v>1.79</v>
+        <v>4.33</v>
       </c>
       <c r="AM3">
-        <v>1.79</v>
+        <v>4.33</v>
       </c>
       <c r="AN3">
-        <v>-0.9072164948453609</v>
+        <v>-1.194756554307116</v>
       </c>
       <c r="AO3">
-        <v>-23.01675977653631</v>
+        <v>-5.658198614318707</v>
       </c>
       <c r="AP3">
-        <v>0.1237113402061855</v>
+        <v>-0.3108614232209737</v>
       </c>
       <c r="AQ3">
-        <v>-23.01675977653631</v>
+        <v>-5.658198614318707</v>
       </c>
     </row>
   </sheetData>
